--- a/Data_clean/MCAS/Estados_US/Edos_USA_2017/NEW_HAMPSHIRE_2017.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2017/NEW_HAMPSHIRE_2017.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C2">
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -428,7 +438,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C5">
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -501,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -542,7 +577,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Tepehuanes</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Total</t>
@@ -695,12 +775,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C24">
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -724,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C26">
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -768,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -814,7 +924,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C32">
@@ -825,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Acatepec</t>
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -851,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mártir de Cuilapan</t>
+          <t>Mártir De Cuilapan</t>
         </is>
       </c>
       <c r="C35">
@@ -864,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tixtla de Guerrero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C36">
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Zapotitlán Tablas</t>
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -934,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -954,7 +1104,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C42">
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -978,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cuautitlán de García Barragán</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C44">
@@ -991,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -1004,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1017,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -1030,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1061,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -1074,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1118,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1149,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1180,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -1193,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Los Ramones</t>
@@ -1206,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -1219,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1250,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C63">
@@ -1263,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Monjas</t>
@@ -1276,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>San Juan Quiahije</t>
@@ -1289,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>San Juan Quiotepec</t>
@@ -1302,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -1315,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Santa Cruz Zenzontepec</t>
@@ -1328,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1359,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -1372,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1385,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -1398,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1418,7 +1698,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C75">
@@ -1429,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -1442,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C77">
@@ -1455,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1468,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1499,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -1512,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -1525,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1556,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1576,7 +1896,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ixhuatlán del Sureste</t>
+          <t>Ixhuatlán Del Sureste</t>
         </is>
       </c>
       <c r="C86">
@@ -1587,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C87">
@@ -1600,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1631,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -1644,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -1657,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -1670,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -1683,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1706,76 +2061,6 @@
       </c>
       <c r="D95">
         <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 826,856</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Junio de 2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
